--- a/EKG_Kalite_Yönetim_Sistemi/13_Giriş Lojistiği ve Depolama/02_ILG2 - Tedarik Alarmı, EDI ve Protokoller/EKG-LOJ-MTR-05_teslimat_takip_ve_gelen_malzeme_alarm_matrisi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/13_Giriş Lojistiği ve Depolama/02_ILG2 - Tedarik Alarmı, EDI ve Protokoller/EKG-LOJ-MTR-05_teslimat_takip_ve_gelen_malzeme_alarm_matrisi.xlsx
@@ -797,7 +797,8 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="2"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-LOJ-MTR-05&amp;C&amp;"Arial,Regular"&amp;11Teslimat Takip ve Gelen Malzeme Alarm Matrisi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 03.06.2026 | Revizyon: 07.09.2026
+Revizyon nedeni: Teslimat formülleri eksik ve geçersiz girdilere göre düzeltildi; varış ve aksiyon alanları eklendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -958,7 +959,8 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="2"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-LOJ-MTR-05&amp;C&amp;"Arial,Regular"&amp;11Teslimat Takip ve Gelen Malzeme Alarm Matrisi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 03.06.2026 | Revizyon: 07.09.2026
+Revizyon nedeni: Teslimat formülleri eksik ve geçersiz girdilere göre düzeltildi; varış ve aksiyon alanları eklendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>